--- a/images/gallery.xlsx
+++ b/images/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="257">
   <si>
     <t>id</t>
   </si>
@@ -2370,6 +2370,678 @@
 It’s time for “harvesting” again
 I have a bad feeling about this</t>
   </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>カブト型餌管理区画</t>
+  </si>
+  <si>
+    <t>Kabuto Feed Unit</t>
+  </si>
+  <si>
+    <t>26.04.11</t>
+  </si>
+  <si>
+    <t>ブウウウン
+殻の内部で何かが回っている
+今日も私は席につき
+ヘルメットを被り端末を開く
+昨晩の飲み会のせいか
+皆どこか調子が悪そうだ
+「餌の消費量が増えています」
+「ああ増やせ この個体はまだ若い」
+カタカタ ピーピー
+入力するたび
+生体情報が吸い上げられていく
+体の奥でエンジンが回る
+ドクン
+中央が脈打つ
+餌を育てるにも時間がかかる
+何をするにももう時間が足りない
+間に合ってくれ
+次は私じゃないことを</t>
+  </si>
+  <si>
+    <t>Buuuuun
+Something is turning
+inside the shell
+I take my seat as always
+put on my helmet
+and open the terminal
+Maybe it’s from last night’s drinks
+everyone looks slightly off
+“The feed consumption is increasing”
+“Then raise it this unit is still young”
+Click clack Beep beep
+With every input
+biometric data is being drawn out
+Deep inside my body
+an engine begins to turn
+Thump
+The core pulses
+It takes time to grow the feed
+There’s not enough time for anything anymore
+Please make it in time
+Next time
+I hope
+it isn’t me</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>脈動する鉄路</t>
+  </si>
+  <si>
+    <t>Pulsating Railway</t>
+  </si>
+  <si>
+    <t>26.04.12</t>
+  </si>
+  <si>
+    <t>よく来たね
+この星へようこそ人間
+君たちは輸送をしているつもりだが
+運ばれているのは別のものだ
+ゴウウウン
+列車が通るたび
+大地は静かに脈打つ
+その管は資源ではない
+我々の神経だ
+君たちの仕事は美しい
+規則正しく
+疑いもせずに動く
+だから気づかない
+荷の中身も
+行き先も
+すべてはこちら側にあることを
+安心していい
+君はもう役割を得ている
+次は君が運ばれる番だ</t>
+  </si>
+  <si>
+    <t>Welcome
+to this planet, human
+You believe you are transporting goods
+but something else is being carried
+Gooouuun
+Each time the train passes
+the ground quietly pulses
+Those tubes are not resources
+they are our nerves
+Your work is beautiful
+precise
+and without doubt
+That is why you never notice
+what lies inside the cargo
+nor where it is headed
+Everything
+belongs to this side
+Do not worry
+you already have a role
+Next
+it will be your turn to be carried</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>増殖管理室</t>
+  </si>
+  <si>
+    <t>Proliferation Control Room</t>
+  </si>
+  <si>
+    <t>26.04.14</t>
+  </si>
+  <si>
+    <t>今日の増殖率は？
+少し上げました 
+昨日よりもよく泳いでいます
+密度が高い 崩れるぞ
+それはあなたの判断ですか？
+ブウウウン
+上から赤がゆっくりと揺れる
+その時
+画面の数値が一斉に乱れた
+来る
+カタカタ
+指が止まらない
+何がです？
+ドキン
+静かに動くな
+液体の奥で何かが反転する
+食われるぞ
+彼が来た</t>
+  </si>
+  <si>
+    <t>What is today’s growth rate？
+I raised it slightly
+They are swimming better than yesterday
+The density is too high it will collapse
+Is that your judgment？
+Buuuuuun
+The red liquid slowly sways from above
+At that moment
+All the numbers on the screen begin to distort
+It’s coming
+Katakata
+My fingers won’t stop
+What is it？
+Thump
+Stay still don’t move
+Something turns deep within the liquid
+It will eat you
+He has arrived</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>生体再現プロトコル</t>
+  </si>
+  <si>
+    <t>Bio Rebuild Protocol</t>
+  </si>
+  <si>
+    <t>26.04.16</t>
+  </si>
+  <si>
+    <t>文明が滅んで
+どれほど経っただろうか
+私に残された任務は「再生」
+山奥に残された小さなラボで
+私は記録を読み続ける
+カタカタと円盤が回り
+過去の生物が断片的に
+浮かび上がってくる
+ぷしゅううん
+それらを組み合わせ
+私は形にする
+かなり近い再現のはずだ
+皿の上でそれは
+ゆっくりと動き出す
+ぼたぼた
+生命は確かに戻りつつある
+もうすぐ文明は
+再生されるだろう
+私は誇りを持っている
+ただ一つ気になるのが
+記録のどこにも
+人間の定義がないことだ</t>
+  </si>
+  <si>
+    <t>How long has it been
+since civilization fell
+The mission left to me is
+“reconstruction”
+In a small lab left deep in the mountains
+I continue reading the records
+Click clack
+the disk spins
+Fragments of past life begin to surface
+Pshhhhh
+I combine them
+and give them form
+It should be a close reconstruction
+On the plate
+it slowly begins to move
+Drip… drip…
+Life is certainly returning
+Soon, civilization
+will be restored
+I take pride in this mission
+But there is one thing that troubles me
+Nowhere in the records
+is there a definition of “human”</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>洞窟インターフェース</t>
+  </si>
+  <si>
+    <t>Cave Interface</t>
+  </si>
+  <si>
+    <t>26.04.18</t>
+  </si>
+  <si>
+    <t>洞窟の奥で
+毛皮をまとった彼らは端末を開き
+静かに観測を続けている
+石の床の装置が光り
+脳を開かれた個体が
+都市の信号を読み取る
+ウホホウ
+カタカタと骨の指で
+原始の手つきのまま
+未来の記録を打ち込む
+外では螺旋の街が脈打ち
+空は信号で満たされている
+槍と火の種がそれを解析する
+都市が現実かどうかは分からない
+道具だけが進化し続け
+理解は置き去りにされた
+これは再生か残響か
+観測が止まるその瞬間
+すべては静かに消える</t>
+  </si>
+  <si>
+    <t>Deep within the cave
+Clad in fur, they open their terminals
+And continue their quiet observation
+Devices embedded in the stone floor glow
+An opened brain emits light
+Reading the signals of the city
+Uhohou
+With a clatter of bone fingers
+Their primitive gestures unchanged
+They input records of the future
+Outside, a spiral city pulses
+The sky is filled with signals
+Spear-and-fire beings analyze it all
+No one knows if the city is real
+Only the tools keep evolving
+Understanding has been left behind
+Is this reconstruction or an echo
+The moment observation ceases
+Everything fades away in silence</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>Bio Vendor</t>
+  </si>
+  <si>
+    <t>26.04.23</t>
+  </si>
+  <si>
+    <t>今日も男は自販機の前に立つ
+ネオンの奥で生体が静かに蠢く
+チャリン
+コインを入れると
+奥の個体がゆっくりと口を開く
+彼は迷いなく餌を差し込む
+「今日も腹減ってるな」
+ズズズ
+触手が指先に絡みつく
+周囲の機械も同時に脈打ち
+都市全体が呼吸しているようだった
+ここでは誰も疑問を持たない
+何を買い何に与えているのか
+気づけば端末に
+「次回給餌対象」の文字が浮かぶ
+その番号の末尾は
+自分の社員番号だった
+この餌？ ああ気にするな 次は俺が食われる番だ</t>
+  </si>
+  <si>
+    <t>Today, the man stands in front of the vending machine again
+Behind the neon, a living entity quietly writhes
+Clink
+As he inserts the coin
+The creature inside slowly opens its mouth
+Without hesitation, he feeds it
+“Hungry again today, huh”
+Zzzzzz
+A tentacle coils around his fingertips
+The surrounding machines begin to pulse in unison
+As if the entire city were breathing
+No one here questions it
+What they are buying, and what they are feeding
+Before he knows it
+A message appears on the terminal
+‘Next Feeding Subject’
+The number ends with
+His own employee ID
+“This feed? Ah, don’t worry
+Next time… I’m the one being eaten</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>忍びの駄菓子商店</t>
+  </si>
+  <si>
+    <t>Shinobi Dagashi Shop</t>
+  </si>
+  <si>
+    <t>26.04.25</t>
+  </si>
+  <si>
+    <t>いらっしゃい
+今日も記憶を買いに来たのか
+駄菓子の棚は左
+カセットはその隣
+サーモンの刺身は今朝入ったばかりだ
+ここでは全部同じ商品だ
+甘い夏休みも
+初めて失恋した夜も
+晩飯の焼き鮭もな
+カタカタ
+奥の機械が今日も蒸気を吐く
+忘れたいなら預ければいい
+思い出したいなら少し高い
+私はただ
+それを量って包むだけだ
+ただ最近
+自分の記憶だけが
+棚のどこにも見つからない</t>
+  </si>
+  <si>
+    <t>Welcome
+Came to buy memories again today?
+The dagashi shelf is on the left
+The cassette tapes are right next to it
+The salmon sashimi came in fresh this morning
+Here, they are all the same product
+Sweet summer vacations
+The night of your first heartbreak
+Even grilled salmon for dinner
+Clatter clatter
+The machine in the back exhales steam again today
+If you want to forget
+Just leave it here
+If you want to remember
+It costs a little more
+I simply
+Weigh it and wrap it for you
+But lately
+I can’t seem to find
+My own memories anywhere on these shelves</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>満月会議</t>
+  </si>
+  <si>
+    <t>Full Moon Conference</t>
+  </si>
+  <si>
+    <t>26.04.26</t>
+  </si>
+  <si>
+    <t>満月が最も近づく夜
+この町では皆が自然に席へ向かう
+五重塔の灯りが揺れ
+雲の底からぞろぞろと
+古い者たちが姿を現す
+鹿の頭をした会社員
+あれはもともと
+この土地を守る神だった
+狼の頭をした男もまた
+災いを司る邪悪神のひとりだ
+今は皆スーツを着て
+静かに同じ鍋を囲んでいる
+今年は誰を残し
+何を滅ぼすのか
+酒が注がれ
+誰も逆らわずに耳を澄ます
+ヤンマーサーカイエルベン
+まずい
+狩りの合図だ</t>
+  </si>
+  <si>
+    <t>On the night when the full moon draws closest
+everyone in this town naturally heads to their seat
+The lights of the five-story pagoda sway
+and from beneath the clouds
+the old ones slowly emerge
+The salaryman with the head of a deer
+was once
+a god who protected this land
+The man with the head of a wolf as well
+is one of the evil gods
+who governs calamity
+Now they all wear suits
+and quietly gather around the same hot pot
+Who will remain this year
+and what will be destroyed
+Sake is poured
+and no one resists
+they simply listen closely
+Yanmaa Sākai Eruben
+This is bad
+It is the signal for the hunt</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>世界管理課</t>
+  </si>
+  <si>
+    <t>World Management Division</t>
+  </si>
+  <si>
+    <t>26.04.29</t>
+  </si>
+  <si>
+    <t>毎朝八時
+私は定時で神になる
+ネクタイを締め
+端末を立ち上げると
+都市の鼓動が始まる
+カタカタ
+出生率を少し下げ
+台風を西へずらし
+誰かの告白を成功させる
+巨大な蟹は
+私の判断を静かに飲み込み
+緑の粘液を街へ流していく
+誰も知らない
+この世界は
+私の残業で保たれている
+ただ最近
+退勤前になると画面にこう出る
+Make them work harder.
+You know how many times we've had to start over, don't you?</t>
+  </si>
+  <si>
+    <t>Every morning at eight
+I become a god on time
+I tighten my tie
+power on the terminal
+and the city begins to pulse
+Clack clack
+I lower the birth rate a little
+shift the typhoon farther west
+make someone’s confession succeed
+The giant crab
+quietly absorbs my decisions
+and sends green liquid through the city
+No one knows
+this world survives
+because of my overtime
+But lately
+right before I leave work
+the screen always shows this
+Make them work harder.
+You know how many times we've had to start over, don't you?</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>根系インターフェース</t>
+  </si>
+  <si>
+    <t>Root Interface</t>
+  </si>
+  <si>
+    <t>26.05.15</t>
+  </si>
+  <si>
+    <t>最近よく眠れる
+以前は薬がないと
+眠れなかったのに
+今は夜になると自然に意識が落ちる
+この研究に参加して
+もう三年になる
+最初は植物の根と
+脳内神経を接続するだけだった
+カタカタ
+端末を打つたび
+内部で葉がわずかに揺れる
+最近は土の湿度も分かる
+雨が近づくと頭の奥が静かに脈打つ
+不思議と嫌な気分ではない
+以前より
+人を嫌いにならなくなった
+皆どこかで
+同じ根につながっている気がする
+ねえ
+人間の体って
+確か緑色が普通だったよね
+うん</t>
+  </si>
+  <si>
+    <t>"Recently, I've been sleeping well.
+I used to need medication
+just to fall asleep,
+but now when night comes,
+my consciousness fades naturally.
+It's been three years
+since I joined this research project.
+At first,
+all we did was connect
+plant roots to neural pathways in the brain.
+Clack clack
+Every time I type at the terminal,
+the leaves inside gently tremble.
+Lately,
+I can even sense the moisture in the soil.
+When rain approaches,
+something deep in my head pulses quietly.
+Strangely,
+I don't mind it.
+Compared to before,
+I don't seem to hate people as much anymore.
+It feels like somewhere,
+we're all connected
+to the same roots.
+Hey...
+Human bodies
+were supposed to be green,
+weren't they?
+Yeah."</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>Shrimp Inside</t>
+  </si>
+  <si>
+    <t>26.05.16</t>
+  </si>
+  <si>
+    <t>ここは頭部内流通センターだ
+端末を操作し
+ニューメンスを入力する
+カタカタ
+すると感情炉が脈打ち
+甲殻ユニットが
+静かに起動する
+怒り 不安 欲望
+それらは整理され
+各人格へ配送されていく
+現代人の頭部に
+初めて潜り込んだのは
+いつだったか
+ちょっと待って
+もしかして僕の頭の中にも
+海老がいるのかしら</t>
+  </si>
+  <si>
+    <t>This is the Cranial Distribution Center
+Operators manipulate the terminals
+and input the Newmens
+clack clack
+Then the emotional furnace begins to pulse
+and the crustacean units
+quietly come online
+Anger Anxiety Desire
+all of it is sorted
+and distributed to each personality
+No one remembers
+when humanity first began
+slipping inside the modern human mind
+Wait a second
+Does that mean
+there’s a shrimp living inside my head too?</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>祈りは支払いではない</t>
+  </si>
+  <si>
+    <t>Prayer Is Not Payment</t>
+  </si>
+  <si>
+    <t>26.05.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">まだ支払いは終わっていない
+君たちにどれだけの文明を
+授けたと思っている
+火を与え
+数を与え
+星を読む目を与えた
+なのに君たちは
+土を掘り水を奪い
+同じ骨を何度も燃やしている
+祈りは届いている
+だが支払いではない
+記録を照合する
+進化値は不足
+信仰値だけが過剰
+これ以上待つことはできない
+君たちは
+君たちのままではいけない
+作り変えなければならない
+ブウウン
+砂の下で古い腹部が開く
+スパイダ・オブ・ネッツ
+最終フェーズを発令だ
+空に白い網を降ろせ
+</t>
+  </si>
+  <si>
+    <t>"まだ支払いは終わっていない
+君たちにどれだけの文明を
+授けたと思っている
+火を与え
+数を与え
+星を読む目を与えた
+なのに君たちは
+土を掘り水を奪い
+同じ骨を何度も燃やしている
+祈りは届いている
+だが支払いではない
+記録を照合する
+進化値は不足
+信仰値だけが過剰
+これ以上待つことはできない
+君たちは
+君たちのままではいけない
+作り変えなければならない
+ブウウン
+砂の下で古い腹部が開く
+スパイダ・オブ・ネッツ
+最終フェーズを発令だ
+空に白い網を降ろせ
+"</t>
+  </si>
 </sst>
 </file>
 
@@ -3906,12 +4578,24 @@
       <c r="Y32" s="3"/>
     </row>
     <row r="33">
-      <c r="A33" s="4"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
+      <c r="A33" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>192</v>
+      </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -3933,12 +4617,24 @@
       <c r="Y33" s="3"/>
     </row>
     <row r="34">
-      <c r="A34" s="4"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
+      <c r="A34" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>198</v>
+      </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -3960,12 +4656,24 @@
       <c r="Y34" s="3"/>
     </row>
     <row r="35">
-      <c r="A35" s="4"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
+      <c r="A35" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>204</v>
+      </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -3987,12 +4695,24 @@
       <c r="Y35" s="3"/>
     </row>
     <row r="36">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="A36" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>210</v>
+      </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4014,12 +4734,24 @@
       <c r="Y36" s="3"/>
     </row>
     <row r="37">
-      <c r="A37" s="4"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
+      <c r="A37" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>216</v>
+      </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -4041,12 +4773,24 @@
       <c r="Y37" s="3"/>
     </row>
     <row r="38">
-      <c r="A38" s="4"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
+      <c r="A38" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>221</v>
+      </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -4068,12 +4812,24 @@
       <c r="Y38" s="3"/>
     </row>
     <row r="39">
-      <c r="A39" s="4"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
+      <c r="A39" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>227</v>
+      </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -4095,12 +4851,24 @@
       <c r="Y39" s="3"/>
     </row>
     <row r="40">
-      <c r="A40" s="4"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
+      <c r="A40" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>233</v>
+      </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
@@ -4122,12 +4890,24 @@
       <c r="Y40" s="3"/>
     </row>
     <row r="41">
-      <c r="A41" s="4"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
+      <c r="A41" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>239</v>
+      </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4149,12 +4929,24 @@
       <c r="Y41" s="3"/>
     </row>
     <row r="42">
-      <c r="A42" s="4"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
+      <c r="A42" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>245</v>
+      </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
@@ -4176,12 +4968,24 @@
       <c r="Y42" s="3"/>
     </row>
     <row r="43">
-      <c r="A43" s="4"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
+      <c r="A43" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>250</v>
+      </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
@@ -4203,12 +5007,24 @@
       <c r="Y43" s="3"/>
     </row>
     <row r="44">
-      <c r="A44" s="4"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
+      <c r="A44" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>

--- a/images/gallery.xlsx
+++ b/images/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="292">
   <si>
     <t>id</t>
   </si>
@@ -3017,30 +3017,400 @@
 </t>
   </si>
   <si>
-    <t>"まだ支払いは終わっていない
-君たちにどれだけの文明を
-授けたと思っている
-火を与え
-数を与え
-星を読む目を与えた
-なのに君たちは
-土を掘り水を奪い
-同じ骨を何度も燃やしている
-祈りは届いている
-だが支払いではない
-記録を照合する
-進化値は不足
-信仰値だけが過剰
-これ以上待つことはできない
-君たちは
-君たちのままではいけない
-作り変えなければならない
+    <t>The payment is not yet complete.
+Do you understand
+how much civilization
+we have bestowed upon you?
+We gave you fire.
+We gave you numbers.
+We gave you eyes to read the stars.
+And yet,
+you dig into the soil,
+steal the water,
+and burn the same bones
+again and again.
+Your prayers have reached us.
+But prayer is not payment.
+Cross-checking the records.
+Evolution value: insufficient.
+Faith value: excessive.
+We can wait no longer.
+You must not remain
+as you are.
+You must be remade.
+Bwoooom.
+Beneath the sand,
+the ancient abdomen opens.
+Spider of Nets.
+Final phase is now authorized.
+Lower the white web
+over the sky.</t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>やさしい案内者</t>
+  </si>
+  <si>
+    <t>A Gentle Guide</t>
+  </si>
+  <si>
+    <t>26.05.24</t>
+  </si>
+  <si>
+    <t>赤い提灯の下
+着物の女たちが
+静かに運ばれていた  
+ベルトコンベアが  
+彼女たちを運ぶ  
+そばを進む爬虫類は  
+監視役であり案内役でもあった  
+一匹が女にそっと囁く  
+怖がらなくていい
+私はあなたを守るためにいる  
+さああの寺までいきましょう
+霧の奥に古い寺が  
+ゆっくり現れた  
+ここが 終わりなの？  
+門が開くと  
+畳の下に星空が広がった  
+寺は宇宙船だったのだ
+爬虫類たちは囁いた
+無事に届けることができました
+孵化場へようこそ</t>
+  </si>
+  <si>
+    <t>Beneath the red lanterns,
+women in kimono
+were carried in silence.
+The conveyor belt
+kept moving them forward.
+The reptiles walking beside them
+were both guards
+and guides.
+One of them softly whispered
+to a woman.
+"Do not be afraid.
+I am here to protect you.
+Now, let us go to that temple."
+Deep within the mist,
+an old temple
+slowly appeared.
+"Is thisthe end?"
+As the gate opened,
+a field of stars spread out
+beneath the tatami floor.
+The temple
+was a spaceship.
+The reptiles whispered,
+"We have delivered them safely."
+"Welcome to the hatchery."</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>砂海の案内人</t>
+  </si>
+  <si>
+    <t>Guide of the Sand Sea</t>
+  </si>
+  <si>
+    <t>26.05.30</t>
+  </si>
+  <si>
+    <t>かつてここは海だった
+今は砂だけが広がり
+あいつらが現れた
+私の役は案内人
+迷い込んだ人間を
+砂海の奥へ導くこと
+ガシュンガシュン
+巨大な脚が砂を踏むたび
+古い都市が少しずつ
+沈んでいく
+あ いた
+やあ迷いこんだのかい
+さあさ
+お乗りになっておくんなまし
+怖がらなくていい
+あの蟹は人を食べない
+ただ運ぶだけ
+砂海の奥には
+古いケーブルが眠っている
+そこへこの人間を
+接続すれば
+ようやく揃うわ
+海を戻すための
+最後の記憶が</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Once this place was the sea
+Now only sand stretches out
+and those things appeared
+My role is guide
+to lead lost humans
+deeper into the sand sea
+Gashun gashun
+Each time those giant legs
+step into the sand
+the old city slowly sinks
+Ah there you are
+Hello there
+did you lose your way
+Come now
+please climb aboard
+No need to be afraid
+that crab does not eat people
+It only carries them
+Deep within the sand sea
+old cables are sleeping
+Once I connect
+this human to them
+everything will finally be complete
+The final memory
+needed to bring back the sea
+</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>記憶果実</t>
+  </si>
+  <si>
+    <t>Memory Fruit</t>
+  </si>
+  <si>
+    <t>26.06.06</t>
+  </si>
+  <si>
+    <t>こちらは昭和期に発見された
+記憶果実の断面標本です
+当時の研究者たちは果実の種子に
+人間の記憶を保存できると考えました
+キュパーン
+奇妙な研究は進み
+後に取り返しのつかない収穫へとつながります
+UFOが通過するたび
+熟した記憶が静かに収穫されました
+はい
+本日ご来館いただいた皆様
+お察しがよろしいようで
+あなたがたはその記憶を元に
+パーフィーと融合された人間なのです
+よろしくどうぞ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here we have a cross-sectional specimen
+of a Memory Fruit discovered
+during the Showa era
+Researchers at the time believed
+human memories could be stored
+inside the seeds of the fruit
+Kyupaan
+The strange research continued
+and eventually led to
+an irreversible harvest
+Whenever a UFO passed overhead
+ripe memories were quietly harvested
+Yes
+To all of you visiting us today
+it seems you have already noticed
+You are humans created by fusing
+those memories with Parfy
+A pleasure to have you here
+</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>人間退職</t>
+  </si>
+  <si>
+    <t>Resignation from Humanity</t>
+  </si>
+  <si>
+    <t>人間でいるには
+この仕事は少し長すぎた
+矛盾にも不条理にも
+いちいち傷ついていた頃は
+まだ柔らかい皮膚をしていた
+だが安心してほしい
+会社は私を見捨てなかった
+働きやすい身体へ変えてくれたのだ
+感情は薄く
+顎は硬く
+命令には従順に
+退職届は出していない
+その代わり
+先月脱皮届を提出した
+課長は笑って言った
+おめでとう君もこれで一人前だ
+私は静かにうなずいた
+もう返事をするための口は
+残っていなかった</t>
+  </si>
+  <si>
+    <t>I had been doing this job
+for a little too long
+to remain human
+Back when every contradiction
+and every absurdity
+still wounded me
+my skin was still soft
+But don’t worry
+the company did not abandon me
+It changed me
+into a body
+better suited for work
+My emotions became thin
+my jaws became hard
+and I became obedient to orders
+I did not submit
+a resignation letter
+Instead
+last month
+I submitted a molting notice
+My manager smiled and said
+Congratulations
+Now you’re finally one of us
+I nodded quietly
+There was no longer
+a mouth left
+with which to answer</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>表情調合室</t>
+  </si>
+  <si>
+    <t>Face Blending Room</t>
+  </si>
+  <si>
+    <t>26.06.07</t>
+  </si>
+  <si>
+    <t>都市には置けないから
+森の奥深くにこのマシンを作った
+ここは表情調合室だ
+笑顔 怒り 不安 安堵 諦め
+それらを少しずつ混ぜ
+無機質な顔面へ注入していく
+ハロハローウ
+画面の中の顔が
+ひとつずつ反応するが
+まだ硬い
+完成には彼らのエキスがいる
+都市で採取された感情は
+地中のケーブルを通ってここまで送られてくる
+通勤中のため息
+会議中の作り笑い
+深夜のエレベーターで消えた顔
+それらを濾過し 混ぜ合わせ
+表情として再構成する
+だれのために
+こんな事をやっているのか
+このケーブル
+俺にもつながってるだろ
+分かるだろ
+なぁ</t>
+  </si>
+  <si>
+    <t>I couldn’t place this machine in the city,
+so I built it deep in the forest.
+This is the Expression Blending Room.
+Smiles, anger, anxiety, relief, resignation.
+I mix them little by little,
+then inject them into inorganic faces.
+Hello-hellooo.
+The faces on the screen
+react one by one,
+but they are still stiff.
+To complete them,
+I need their essence.
+The emotions harvested in the city
+are sent here through cables
+running beneath the ground.
+Sighs during the morning commute.
+Fake smiles in meetings.
+Faces that disappeared
+inside late-night elevators.
+I filter them,
+blend them together,
+and reconstruct them as expressions.
+Who am I doing
+something like this for?
+This cable
+is connected to me too.
+You understand, don’t you?
+Hey.</t>
+  </si>
+  <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>人育ちの魚</t>
+  </si>
+  <si>
+    <t>Human-Grown Fish</t>
+  </si>
+  <si>
+    <t>26.06.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">私が夜な夜なこっそり魚をあれに変えているとは知らないだろう
 ブウウン
-砂の下で古い腹部が開く
-スパイダ・オブ・ネッツ
-最終フェーズを発令だ
-空に白い網を降ろせ
-"</t>
+円盤の光が落ちる
+私は包丁を入れ
+骨を抜き
+静かに形を整える
+作業自体は難しくない
+ただ材料が特殊なのだ
+この魚は深海ではなく
+街で獲れる
+会社の会議室
+病院の待合室
+満員電車
+そういう場所で育つ
+奥の座敷では
+今夜も客が待っている
+皆偉い人たちだ
+私が皿を差し出すと
+一人が満足そうに笑った
+やはりここのは違う
+パームステンスマイマイ
+最近のはよく育つ
+</t>
+  </si>
+  <si>
+    <t>Most people passing by would never know
+that night after night, I secretly turn fish into that.
+Bwoooom.
+The light from the saucer falls onto the table.
+I make a cut with the knife,
+remove the bones,
+and quietly shape it into form.
+The work itself isn't difficult.
+It's the ingredients that are unusual.
+These fish aren't caught in the deep sea.
+They're caught in the city.
+Corporate meeting rooms.
+Hospital waiting areas.
+Crowded commuter trains.
+Those are the places where they grow.
+In the tatami room beyond,
+tonight's guests are already waiting.
+Important people, every one of them.
+When I place the dish before them,
+one man smiles with satisfaction.
+"As expected. Yours are different."
+"Palmsten Smimai."
+"The recent ones have been growing remarkably well."</t>
   </si>
 </sst>
 </file>
@@ -5046,12 +5416,24 @@
       <c r="Y44" s="3"/>
     </row>
     <row r="45">
-      <c r="A45" s="4"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
+      <c r="A45" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>262</v>
+      </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
@@ -5073,12 +5455,24 @@
       <c r="Y45" s="3"/>
     </row>
     <row r="46">
-      <c r="A46" s="4"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
+      <c r="A46" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>268</v>
+      </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
@@ -5100,12 +5494,24 @@
       <c r="Y46" s="3"/>
     </row>
     <row r="47">
-      <c r="A47" s="4"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
+      <c r="A47" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>274</v>
+      </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
@@ -5127,12 +5533,24 @@
       <c r="Y47" s="3"/>
     </row>
     <row r="48">
-      <c r="A48" s="4"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
+      <c r="A48" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>279</v>
+      </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
@@ -5154,12 +5572,24 @@
       <c r="Y48" s="3"/>
     </row>
     <row r="49">
-      <c r="A49" s="4"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
+      <c r="A49" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>285</v>
+      </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
@@ -5181,12 +5611,24 @@
       <c r="Y49" s="3"/>
     </row>
     <row r="50">
-      <c r="A50" s="4"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
+      <c r="A50" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>291</v>
+      </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>

--- a/images/gallery.xlsx
+++ b/images/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="340">
   <si>
     <t>id</t>
   </si>
@@ -1503,7 +1503,7 @@
   <si>
     <t>あれはいつの頃か
 俺がまだ体を持っていた頃
-この寺に調査で来た
+この神社に調査で来た
 ただの点検のはずだった
 古い機械と建物
 確認するだけだった
@@ -3411,6 +3411,435 @@
 "As expected. Yours are different."
 "Palmsten Smimai."
 "The recent ones have been growing remarkably well."</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>OS更新日</t>
+  </si>
+  <si>
+    <t>OS Update Day</t>
+  </si>
+  <si>
+    <t>26.06.24</t>
+  </si>
+  <si>
+    <t>今日はOS更新の日だ
+Win10のサポートが切れるらしい
+私は朝早くから洞窟へ向かった
+ブウウン
+円盤が静かに降りてくる
+白い服の保守員が降り立ち、巨大なコンピューターを起動した
+次の方
+私は腕を差し出す
+保守員がケーブルを接続する
+バックアップ取ってる？
+あ、はい
+よかった
+前回の更新で弟が魚になってたから
+よくある互換性の問題ですね
+保守員は慣れた手つきで呟いた
+更新が終わる頃には、
+遠くの街でも少しだけ世界が変わっている。
+原始人がいてその先に現代人がいる
+ノンノンノン
+私たちは同じ時間を生きている。
+誰かの仕事で
+世界は今日も静かに更新されているのだ</t>
+  </si>
+  <si>
+    <t>Today is OS Update Day
+I heard support for Windows 10 is ending
+I headed to the cave early that morning
+Bwoooom
+A flying saucer quietly descended from the sky
+A maintenance worker in white stepped out and powered on the giant computer
+"Next please"
+I held out my arm
+The technician connected a cable
+"Did you back everything up?"
+"Yes"
+"Good"
+"My younger brother turned into a fish after the last update"
+"That's a fairly common compatibility issue"
+The technician muttered it with the calm voice of someone who had said it countless times before
+By the time the update is complete
+the world changes just a little
+even in the distant cities
+Primitive humans came first
+and modern humans evolved afterward
+"Non non non"
+We are living in the same time
+Because of someone's everyday job
+the world is quietly updated once again today</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>第三送電所</t>
+  </si>
+  <si>
+    <t>The Third Substation</t>
+  </si>
+  <si>
+    <t>26.07.02</t>
+  </si>
+  <si>
+    <t>山中の第三送電所には
+CITYからの欲が
+電力に混じって集まる
+ぬぼわぁ
+で
+あいつがそれを食う
+私は派遣社員のエンジニア
+今日も電力の位相を調整しにきた
+500マイスボルテージを
+350へ下げてっと
+しかし最近の欲はすごいわね
+CITYは一体どうなってんだか
+よっしゃこれで終了
+早く家に帰って
+ファミコンをやろう
+白い霧の向こうで
+あいつが不満そうに瞬いた</t>
+  </si>
+  <si>
+    <t>At the Third Substation
+deep in the mountains
+desire from the CITY gathers
+mixed into the electricity
+Nubowaaah
+And then
+that thing eats it
+I’m a dispatched engineer
+I came here again today
+to adjust the phase of the power
+Lowering the 500 Mice Voltage
+down to 350
+Still
+desire these days is incredible
+what on earth is happening
+to the CITY
+Alright
+that’s done
+I want to get home early
+and play Famicom
+Beyond the white mist
+that thing blinked
+as if dissatisfied</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>釣り人の桟橋</t>
+  </si>
+  <si>
+    <t>The Pier of Fishermen</t>
+  </si>
+  <si>
+    <t>26.07.03</t>
+  </si>
+  <si>
+    <t>この桟橋には二種類の釣り人がいる
+魚を釣る者と
+空に釣られる者だ
+夕暮れになると
+皆どこか落ち着かなくなる
+ブウウン
+円盤が静かに近づく
+よし 食った
+会社員は満面の笑みで両手を広げ
+白い光に勢いよく吸い込まれていった
+周囲の釣り人たちは
+釣果を見守るように静かにうなずく
+魚を釣るより
+誰かに釣られる方が幸せな日もある</t>
+  </si>
+  <si>
+    <t>There are two kinds of fishermen on this pier.
+Those who catch fish
+and those who are caught by the sky.
+As evening falls
+everyone grows a little restless.
+Bwooooom
+A flying saucer quietly approaches.
+Yes
+It took the bait.
+The salaryman spreads his arms with a beaming smile
+and is swiftly pulled into the white beam of light.
+The other fishermen
+silently nod
+as if admiring a fine catch.
+Some days
+being caught
+is happier than catching fish.</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>閉店ドローン</t>
+  </si>
+  <si>
+    <t>Closing Drone</t>
+  </si>
+  <si>
+    <t>26.07.06</t>
+  </si>
+  <si>
+    <t>ふう
+今晩もまた来てしまった
+最初に来たのは
+墓参りの帰りだった
+墓場に提灯が灯ってるんだ
+そりゃ驚くさ
+だけど一杯飲んで
+もっと驚いた
+ここじゃ
+先に逝った同僚と
+酒を飲みながら話せるんだ
+ブウウン
+ああ
+閉店のドローンだ
+あれが来ると
+みんな静かに自分の墓へ帰っていく
+じゃあまた
+店を出るのはいつも私だけだ</t>
+  </si>
+  <si>
+    <t>Phew.
+I ended up coming here again tonight.
+The first time I came
+was after visiting a grave.
+Lanterns glowing in a cemetery—
+yeah, that caught me off guard.
+But after having a drink,
+I was even more surprised.
+Here,
+you can share a drink
+and talk with coworkers
+who passed away before you.
+Bzzzzz...
+Ah.
+That's the closing drone.
+When it arrives,
+everyone quietly returns
+to their own grave.
+See you again.
+I'm always
+the only one who leaves the bar.</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>中央鮮魚街</t>
+  </si>
+  <si>
+    <t>Central Fish Market</t>
+  </si>
+  <si>
+    <t>26.07.09</t>
+  </si>
+  <si>
+    <t>へいらっしゃい
+今日も新鮮な切り身
+入ってますよ
+ファーナム産の甘塩鮭
+どうぞ
+いらっしゃい
+いらっしゃい
+スモークがいいなら
+あの店で買って
+ビールと一緒に飲みたい？
+じゃあ
+あそこの立ち飲み屋がおすすめだ
+好きなものを
+好きな飲み物と一緒に
+好きなだけ
+…
+上が開いてから
+この辺の魚は本当にうまくなった</t>
+  </si>
+  <si>
+    <t>Hey, welcome
+Fresh cuts came in today.
+Lightly salted salmon from Farnham.
+Come on in.
+Step right up.
+Looking for smoked salmon?
+Try the shop over there.
+Want something to go with a beer?
+Then I'd recommend
+the standing bar just down the street.
+Pick whatever you like.
+Pair it with your favorite drink
+and eat as much as you want.
+...
+Come to think of it...
+Ever since
+the sky opened up,
+the fish around here
+have tasted a whole lot better.</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>昭和52年式</t>
+  </si>
+  <si>
+    <t>1977 Model</t>
+  </si>
+  <si>
+    <t>26.07.12</t>
+  </si>
+  <si>
+    <t>今日から宇宙事業部に配属された
+最初に渡されたのは
+一冊のリーフレットだった
+「甲殻生物型ポッドで行く宇宙作業」
+昭和52年から現在まで
+一度も設計変更はありません
+操縦席は口の中
+大気圏で一度脱皮します
+帰還時は尻尾から
+前向きでは帰れません
+…
+午後から実技研修らしい
+私はリーフレットを閉じて
+甲殻生物の口へ向かった</t>
+  </si>
+  <si>
+    <t>Today was my first day in the Space Operations Division.
+The first thing they handed me
+was a small brochure.
+"Space Operations with the Crustacean Bio-Pod"
+Its design has never been changed
+since 1977.
+The cockpit is inside the mouth.
+It molts once
+while passing through the atmosphere.
+For the return trip,
+it enters tail first.
+It cannot come back
+facing forward.
+...
+Apparently,
+practical training starts this afternoon.
+I closed the brochure
+and walked toward the mouth
+of the crustacean.</t>
+  </si>
+  <si>
+    <t>056</t>
+  </si>
+  <si>
+    <t>終身融合制度</t>
+  </si>
+  <si>
+    <t>Lifetime Integration Program</t>
+  </si>
+  <si>
+    <t>26.07.19</t>
+  </si>
+  <si>
+    <t>今日から
+生体インフラ事業部へ配属された
+最初は驚いた
+会社が昆虫だったからだ
+でも慣れる
+人間って
+案外すぐ慣れる
+池の掃除をして
+魚に餌をやって
+サーバーを点検する
+それが私の仕事
+定年まであと二十年
+その頃には
+私もこの昆虫の一部になれるらしい
+部長は
+「羨ましいだろ」と言って笑った
+私も笑った</t>
+  </si>
+  <si>
+    <t>Today was my first day
+in the Bio-Infrastructure Division.
+At first,I was surprised.
+The company was a giant insect.
+But you get used to it.
+Humans...
+adapt much faster than you'd think.
+I clean the pond.
+Feed the fish.
+Inspect the servers.
+That's my job.
+Twenty years until retirement.
+By then,
+they say
+I'll become part of this insect too.
+My manager smiled.
+"You're lucky, you know."
+I smiled too.</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
+    <t>中央神経局</t>
+  </si>
+  <si>
+    <t>Central Nervous Bureau</t>
+  </si>
+  <si>
+    <t>26.07.31</t>
+  </si>
+  <si>
+    <t>地下二千メートルで
+発見された巨人は死んでいた
+脳だけを除いて
+人類は歓喜した
+その脳はどんなスーパーコンピューターより
+速く正確だった
+以来
+都市はその脳を中心に築かれた
+交通も通信も行政も
+すべて巨人が支えている
+私は保守部門の会社員
+毎朝脳へ接続し
+昨日集めた人間の記憶を入力する
+感情や迷いも忘れず送る
+それが思考を安定させるらしい
+詳しいことは私も知らない
+ただ一つ
+新人研修で教わった規則だけは覚えている
+問いかけられても決して
+返事をするな</t>
+  </si>
+  <si>
+    <t>Two kilometersbeneath the ground
+The giant we foundwas dead
+Except for its brain
+Humanity rejoiced
+Its brain was faster and more accurate
+than any supercomputer 
+Since then
+our cities have been built around its brain
+Transportation communications government
+Everything is sustained by the giant
+I work in the maintenance division
+Every morning I connect myself to the brain
+and upload the memories collected from people the day before
+Their emotions Their doubts Nothing is omitted
+They say it keeps the brain thinking steadily
+I don't know how it really works
+But there is one rule
+I still remember from orientation
+If it speaks
+Never answer back</t>
   </si>
 </sst>
 </file>
@@ -5650,12 +6079,24 @@
       <c r="Y50" s="3"/>
     </row>
     <row r="51">
-      <c r="A51" s="4"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
+      <c r="A51" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>297</v>
+      </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
@@ -5677,12 +6118,24 @@
       <c r="Y51" s="3"/>
     </row>
     <row r="52">
-      <c r="A52" s="4"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
+      <c r="A52" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>303</v>
+      </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -5704,12 +6157,24 @@
       <c r="Y52" s="3"/>
     </row>
     <row r="53">
-      <c r="A53" s="4"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
+      <c r="A53" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>309</v>
+      </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
@@ -5731,12 +6196,24 @@
       <c r="Y53" s="3"/>
     </row>
     <row r="54">
-      <c r="A54" s="4"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
+      <c r="A54" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>315</v>
+      </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
@@ -5758,12 +6235,24 @@
       <c r="Y54" s="3"/>
     </row>
     <row r="55">
-      <c r="A55" s="4"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
+      <c r="A55" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
@@ -5785,12 +6274,24 @@
       <c r="Y55" s="3"/>
     </row>
     <row r="56">
-      <c r="A56" s="4"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
+      <c r="A56" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>327</v>
+      </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
@@ -5812,12 +6313,24 @@
       <c r="Y56" s="3"/>
     </row>
     <row r="57">
-      <c r="A57" s="4"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
+      <c r="A57" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>333</v>
+      </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
@@ -5839,12 +6352,24 @@
       <c r="Y57" s="3"/>
     </row>
     <row r="58">
-      <c r="A58" s="4"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
+      <c r="A58" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>339</v>
+      </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>

--- a/images/gallery.xlsx
+++ b/images/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="346">
   <si>
     <t>id</t>
   </si>
@@ -3840,6 +3840,57 @@
 I still remember from orientation
 If it speaks
 Never answer back</t>
+  </si>
+  <si>
+    <t>058</t>
+  </si>
+  <si>
+    <t>第七製造所</t>
+  </si>
+  <si>
+    <t>Facility No. 7</t>
+  </si>
+  <si>
+    <t>26.08.02</t>
+  </si>
+  <si>
+    <t>ようこそ森林第七製造所へ
+ここでは皆様と同じ作業員を製造しております
+都市では騒音や排熱の問題がありますので
+工場は森の奥に建設いたしました
+自然との共生も当社の大切な理念です
+ご覧ください
+作業員たちは毎日一体ずつ組み立てています
+もちろん
+完成した個体が
+自分とよく似ていることに気づく者もおります
+ですが業務に支障はございません
+皆様が今見ている景色も
+中央演算機へ正常に共有されております
+最初の一体は誰が作ったのか
+申し訳ございません
+その資料だけは
+当社にも残っておりません</t>
+  </si>
+  <si>
+    <t>Welcome to Forest Manufacturing Facility No. 7.
+Here, we manufacture workers just like yourselves.
+To avoid noise and excess heat in urban areas,
+this facility was built deep within the forest.
+Living in harmony with nature 
+has always been one of our company's core principles.
+Please take a look.
+Our workers assemble one unit each day.
+Naturally,
+some eventually notice
+that the completed unit looks remarkably similar to themselves.
+However,this has never interfered with their work.
+The scenery you are looking at right now 
+is being properly shared with the Central Processing Unit.
+"Who built the very first one?"
+We sincerely apologize.
+That is the only record
+our company no longer possesses.</t>
   </si>
 </sst>
 </file>
@@ -4124,7 +4175,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="22.63"/>
-    <col customWidth="1" min="5" max="5" width="117.25"/>
+    <col customWidth="1" min="5" max="5" width="93.5"/>
     <col customWidth="1" min="6" max="6" width="36.5"/>
   </cols>
   <sheetData>
@@ -6391,12 +6442,24 @@
       <c r="Y58" s="3"/>
     </row>
     <row r="59">
-      <c r="A59" s="4"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
+      <c r="A59" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>345</v>
+      </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>

--- a/images/gallery.xlsx
+++ b/images/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="388">
   <si>
     <t>id</t>
   </si>
@@ -3854,43 +3854,476 @@
     <t>26.08.02</t>
   </si>
   <si>
-    <t>ようこそ森林第七製造所へ
-ここでは皆様と同じ作業員を製造しております
+    <t>ようこそ
+森林第七製造所へ
+当工場では
+神々へ奉納する個体を製造しております
 都市では騒音や排熱の問題がありますので
 工場は森の奥に建設いたしました
-自然との共生も当社の大切な理念です
 ご覧ください
 作業員たちは毎日一体ずつ組み立てています
+完成した個体は日没前に回収され
+神々へ納品されます
+創業以来一日も欠かしたことはございません
 もちろん
-完成した個体が
-自分とよく似ていることに気づく者もおります
-ですが業務に支障はございません
-皆様が今見ている景色も
-中央演算機へ正常に共有されております
-最初の一体は誰が作ったのか
+作業員たちは何のために納品しているのか知りません
+知る必要がないからです
+神々はどのようなお姿なのですか？
+ご安心ください
+皆様もすでにご覧になっています
+最初の一体は誰が作ったのですか？
 申し訳ございません
 その資料だけは
 当社にも残っておりません</t>
   </si>
   <si>
-    <t>Welcome to Forest Manufacturing Facility No. 7.
-Here, we manufacture workers just like yourselves.
+    <t>Welcome to
+Forest Manufacturing Facility No. 7.
+At this facility,
+we manufacture units to be offered to the Gods.
 To avoid noise and excess heat in urban areas,
-this facility was built deep within the forest.
-Living in harmony with nature 
-has always been one of our company's core principles.
+this factory was built deep within the forest.
 Please take a look.
-Our workers assemble one unit each day.
-Naturally,
-some eventually notice
-that the completed unit looks remarkably similar to themselves.
-However,this has never interfered with their work.
-The scenery you are looking at right now 
-is being properly shared with the Central Processing Unit.
+Our workers assemble one unit every day.
+Each completed unit is collected before sunset
+and delivered to the Gods.
+Not a single day has been missed since the company was founded.
+Of course,
+our workers do not know why the units are delivered.
+There is no need for them to know.
+"What do the Gods look like?"
+Please don't worry.
+You have already seen them.
 "Who built the very first one?"
 We sincerely apologize.
 That is the only record
-our company no longer possesses.</t>
+our company no longer retains.</t>
+  </si>
+  <si>
+    <t>059</t>
+  </si>
+  <si>
+    <t>夜は毎晩</t>
+  </si>
+  <si>
+    <t>Every Night at Night</t>
+  </si>
+  <si>
+    <t>26.08.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「さあ始めようか」
+私は毎晩この屋上で街の周波数を合わせる
+巨大な反射鏡がゆっくり空を向き
+円盤が所定の位置へ入ると
+眠っていた者たちが目を覚ます
+街では幽霊と呼ばれているが
+彼らは誰かの記憶が電波になった姿だ
+仕事は単純
+迷子になった記憶を拾い正しい家へ返してやるだけ
+一つでも取り残せば
+翌朝には誰かが大切な人の顔を思い出せなくなる
+だから私は夜明けまでここを離れない
+朝になる頃には
+皆何事もなかったように今日を生き始める
+私が昨夜
+少しだけ書き換えたことも知らずに
+</t>
+  </si>
+  <si>
+    <t>"Shall we begin?"
+Every night, I climb to this rooftop to tune the city's frequency.
+The giant reflector slowly turns toward the sky.
+Once the disc reaches its designated position,
+those who had been asleep begin to awaken.
+People in the city call them ghosts,
+but they are memories that have taken the form of radio waves.
+The job is simple.
+I gather the memories that have lost their way and return them to where they belong.
+If even one is left behind,
+someone will wake the next morning unable to remember the face of a loved one.
+So I never leave this rooftop until dawn.
+By sunrise,
+everyone goes on with their day as if nothing had happened.
+Never realizing that I rewrote
+just a tiny part of their memories the night before.</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>次元スクラッチ</t>
+  </si>
+  <si>
+    <t>Dimensional Scratch</t>
+  </si>
+  <si>
+    <t>26.08.07</t>
+  </si>
+  <si>
+    <t>ここはCITY38
+今晩もDJが
+三つの次元を同時に回す
+一枚目は江戸
+二枚目は昭和
+三枚目は
+まだ誰も知らない未来
+三つの拍子が重なるとこの街の今日が決まる
+今日は何した何をみた
+神頼みちゃぶ台返し
+いつもどおり
+へい
+気付いたかい
+君の思い出も
+誰かのリミックスだ</t>
+  </si>
+  <si>
+    <t>This is CITY38.
+Tonight again,
+the DJ spins three dimensions at once.
+The first record is Edo.
+The second is Showa.
+The third is
+a future no one has seen yet.
+When the three rhythms overlap,today in this city is decided.
+What did you do today?What did you see?
+Prayers to the gods,flipping the dinner table,
+just like always.
+Hey.
+Did you notice？
+Even your memories
+are somebody else's remix.</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>33日水脈</t>
+  </si>
+  <si>
+    <t>33-Day Water Vein</t>
+  </si>
+  <si>
+    <t>26.08.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">俺は地下水管理会社の社員だ
+仕事は砂漠の水脈を探すこと
+といっても俺が探すわけじゃない
+古い遺跡から採掘されたあの骸骨が探す
+頭にセンサーを繋いで砂漠へ向けておく
+すると突然
+ピカッと
+目が赤く光る
+骸骨の目線の先が水脈
+お宝ドンって訳だ
+あとは掘削班へ場所を伝えて
+水が出るまで掘る
+ただし一つだけ決まりがある
+目が光ってから33日以内に水を掘り当てること
+失敗した場合
+担当者の命は保証されない
+理由は知らない
+入社した時からそういう規則だ
+だから
+骸骨の目が光るたびソワソワする
+ピカッ
+お
+光った
+俺はゆっくり骸骨の目線を追った
+……
+こっち見てる
+</t>
+  </si>
+  <si>
+    <t>I work for a groundwater management company
+My job is to find water veins beneath the desert
+Though I'm not the one who finds them
+That skeleton we dug up from some ancient ruins does
+We hook sensors up to its skull and point it toward the desert
+Then suddenly
+FLASH
+Its eyes glow red
+Wherever the skeleton is looking
+that's where the water is Jackpot
+Then I tell the drilling crew where to dig
+and they keep going until they hit water
+There's just one rule
+Once its eyes light up we have 33 days to find the water
+If we fail
+The person in charge is not guaranteed to survive
+I don't know why
+It's been company policy since the day I joined
+So every time those eyes light up
+I get a little nervous
+FLASH
+Oh
+There it goes
+I slowly followed the skeleton's gaze
+...
+It's looking at me</t>
+  </si>
+  <si>
+    <t>062</t>
+  </si>
+  <si>
+    <t>カサカサ勤務</t>
+  </si>
+  <si>
+    <t>Skitter Shift</t>
+  </si>
+  <si>
+    <t>26.08.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">火星で観測を始めて数ヶ月
+勤務中にビールを呑んでもOKなんて素敵
+最初はどうなることかと思った
+元々ここにいた住人はサソリに変えられちゃってるし
+しかも本人たちはまだ人間だと思ってるみたい
+カサカサ
+まあ
+本人たちが幸せならそれでいいか
+私もここでの暮らし結構気に入ってる
+サソってGO
+カサカサってYO
+毒針まいまい
+田舎の素麺
+真夏に食べとけ思い出マイメン
+...
+うん今日も調子いい
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I've been stationed on Mars for a few months now
+Being allowed to drink beer on the job is pretty amazing
+At first I wasn't sure how things would turn out
+The people who originally lived here have all been turned into scorpions
+And apparently they still think they're human
+Skitter skitter
+Well as long as they're happy I guess that's all that matters
+I'm actually starting to like life out here
+Scorpion, let's GO
+Skitter skitter, YO
+Stingers flying, mai mai
+Country-style somen on standby
+Eat it in midsummer
+Memories with my main man
+...
+Yeah,Everything's looking good today
+</t>
+  </si>
+  <si>
+    <t>063</t>
+  </si>
+  <si>
+    <t>地上会議</t>
+  </si>
+  <si>
+    <t>Surface Meeting</t>
+  </si>
+  <si>
+    <t>26.08.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">長い連休も終わって今日からまた仕事
+憂鬱だよ
+まあ飲みなよ
+明日は地上で会議だったっけ
+そうそう朝から本社
+うわぁ地上かぁ
+ネクタイ乾くの嫌なんだよな
+あ 
+地上会議の申請した？
+今日の17時までだぞ
+うそ
+部長印だけじゃダメ？
+ダメダメ
+あいつの承認いるよ
+同僚が奥を指差した
+巨大な眼球がじっと見ている
+……
+ギョロ
+パチン
+お
+通った
+よかった
+じゃあもう一杯飲んで帰るか
+そうだな
+明日は地上だし
+今のうちにたっぷり濡れとこう
+</t>
+  </si>
+  <si>
+    <t>The long holiday is over, and it's back to work today.
+I'm depressed.
+Come on, have a drink.
+Wasn't the meeting tomorrow up on the surface?
+Yeah, at headquarters first thing in the morning.
+Ugh, the surface...
+I hate it when my tie dries out.
+Oh.
+Did you submit the application for the surface meeting?
+It's due by 5 p.m. today.
+Seriously?
+Isn't the department manager's stamp enough?
+No, no.
+You need his approval.
+My coworker pointed toward the back.
+A giant eyeball was staring at us.
+……
+GLOOR
+BLINK
+Oh.
+It went through.
+Good.
+Let's have one more drink before we head home.
+Yeah.
+We're going up to the surface tomorrow.
+Might as well get nice and soaked while we still can.</t>
+  </si>
+  <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>本体の畑</t>
+  </si>
+  <si>
+    <t>The Farm of the Main Body</t>
+  </si>
+  <si>
+    <t>26.08.23</t>
+  </si>
+  <si>
+    <t>ここの土地なら
+いい畑になると思いますよ
+パーユベンの成長に必要な元素が
+地中にたっぷりありますから
+なるほど
+昆虫型探査機は
+ゆっくりと火星の地表を進んでいく
+しかし皆さん
+よく人間に似せて作られてますね
+最近のモデルは
+触覚まで本体と繋がってますから
+へえ
+じゃあ今
+火星の土を踏んでる感覚も？
+ええ
+ちゃんと感じますよ
+では
+この一帯を栽培区画にしましょう
+ところで
+収穫したパーユベンって
+地球では何に使われてるんです？
+詳しくは知りません
+地中の培養施設へ運ばれて
+何かの培養土になるそうです
+へえ
+何を育ててるんでしょうね</t>
+  </si>
+  <si>
+    <t>This land
+should make good farmland
+The soil is rich in the elements
+Par-yuben needs to grow
+I see
+The insect-shaped exploration vehicle
+slowly moves across the surface of Mars
+Still
+you all look remarkably human
+The newer models
+even have their sense of touch connected to their main bodies
+Huh
+So right now
+you can feel the Martian soil beneath your feet?
+Yes
+I can feel it perfectly
+Then
+let's designate this whole area for cultivation
+By the way
+What is the harvested Par-yuben
+used for back on Earth?
+I don't know the details
+Apparently it's taken to an underground cultivation facility
+and used as some kind of growth medium
+Huh
+I wonder what they're growing down there</t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>脳糸蜘蛛</t>
+  </si>
+  <si>
+    <t>Brainthread Spider</t>
+  </si>
+  <si>
+    <t>26.08.25</t>
+  </si>
+  <si>
+    <t>この砂漠には
+世界中の情報が集まってくる
+こいつのおかげでな
+私は奥の巨大な蜘蛛を指差した
+蜘蛛が吐いた糸を
+砂漠の中へ垂らす
+すると糸は地中を這い
+根を張るように世界中へ伸びていく
+街の会話も
+誰かの記憶も
+昨日の喧嘩も
+全部この糸を伝って戻ってくる
+だが
+集めるだけじゃ意味がない
+蜘蛛の糸に人間の細胞を繋ぎ
+この培養槽で育てる
+そうすると
+世界中の情報を理解する
+新しい生命体の脳ができる
+私は毎日ここで
+脳の成長を見守っている
+カタカタ
+ん？
+侍は昔の人だって？
+何言ってんだ
+今でも次元の間で生きてるぜ
+ほら
+お前が今それを言ったことも
+もう糸から届いてる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information from all over the world
+gathers here in this desert
+All thanks to this guy
+I pointed to the giant spider in the back
+We lower the threads it spins
+into the desert
+Then they crawl underground
+spreading across the world like roots
+Conversations in the city
+someone’s memories
+yesterday’s arguments
+It all travels back here through these threads
+But
+there’s no point in just collecting it
+We connect human cells
+to the spider silk and grow them in this tank
+And then
+we get the brain of a new life-form
+capable of understanding information from all over the world
+Every day
+I sit here and watch the brain grow
+Clack clack
+Hmm?
+You think samurai are people from the past?
+What are you talking about?
+We’re still alive between dimensions
+Look
+Even what you just said
+has already reached me through the threads
+</t>
   </si>
 </sst>
 </file>
@@ -4175,8 +4608,8 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="22.63"/>
-    <col customWidth="1" min="5" max="5" width="93.5"/>
-    <col customWidth="1" min="6" max="6" width="36.5"/>
+    <col customWidth="1" min="5" max="5" width="68.63"/>
+    <col customWidth="1" min="6" max="6" width="47.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6481,12 +6914,24 @@
       <c r="Y59" s="3"/>
     </row>
     <row r="60">
-      <c r="A60" s="4"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
+      <c r="A60" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>351</v>
+      </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -6508,12 +6953,24 @@
       <c r="Y60" s="3"/>
     </row>
     <row r="61">
-      <c r="A61" s="4"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
+      <c r="A61" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>357</v>
+      </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
@@ -6535,12 +6992,24 @@
       <c r="Y61" s="3"/>
     </row>
     <row r="62">
-      <c r="A62" s="4"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
+      <c r="A62" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>363</v>
+      </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
@@ -6562,12 +7031,24 @@
       <c r="Y62" s="3"/>
     </row>
     <row r="63">
-      <c r="A63" s="4"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
+      <c r="A63" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>369</v>
+      </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
@@ -6589,12 +7070,24 @@
       <c r="Y63" s="3"/>
     </row>
     <row r="64">
-      <c r="A64" s="4"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
+      <c r="A64" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>375</v>
+      </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
@@ -6616,12 +7109,24 @@
       <c r="Y64" s="3"/>
     </row>
     <row r="65">
-      <c r="A65" s="4"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
+      <c r="A65" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>381</v>
+      </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
@@ -6643,12 +7148,24 @@
       <c r="Y65" s="3"/>
     </row>
     <row r="66">
-      <c r="A66" s="4"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
+      <c r="A66" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>387</v>
+      </c>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>

--- a/images/gallery.xlsx
+++ b/images/gallery.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="412">
   <si>
     <t>id</t>
   </si>
@@ -4324,6 +4324,245 @@
 Even what you just said
 has already reached me through the threads
 </t>
+  </si>
+  <si>
+    <t>066</t>
+  </si>
+  <si>
+    <t>地下水路市場</t>
+  </si>
+  <si>
+    <t>Underground Waterway Market</t>
+  </si>
+  <si>
+    <t>26.08.29</t>
+  </si>
+  <si>
+    <t>仕事終わりはだいたいここに寄る
+地下街の真ん中にある大きな生け簀
+昔は普通の市場だったらしい
+今では魚もエイも地下水路から勝手に入ってくる
+だから店のおっちゃんたちは
+毎朝ここから適当にすくって店に並べる
+今日も一杯やっていると
+バシャッ
+大きなエイが水面から顔を出した
+お
+今日は近いな
+私がビールを飲みながら眺めていると
+隣の同僚が小声で言った
+あれ昨日辞めた田中さんじゃない？
+……
+確かに似ている
+まあいいか
+おっちゃん
+エイヒレもう一枚</t>
+  </si>
+  <si>
+    <t>After work I usually stop by here
+A huge fish tank right in the middle of the underground market
+Apparently this used to be a normal marketplace
+These days fish and rays just swim in through the underground waterways
+So every morning
+the shopkeepers scoop out whatever they can and put it up for sale
+I was having a drink here again today when
+SPLASH
+A huge ray poked its head out of the water
+Oh
+Pretty close today
+As I watched it over my beer
+my coworker beside me whispered
+Isn't that Tanaka who quit yesterday?
+...
+It does look like him
+Oh well
+Hey boss
+Another plate of grilled stingray fin</t>
+  </si>
+  <si>
+    <t>067</t>
+  </si>
+  <si>
+    <t>虫内勤務</t>
+  </si>
+  <si>
+    <t>Working Inside the Bug</t>
+  </si>
+  <si>
+    <t>2026.8.31</t>
+  </si>
+  <si>
+    <t>2000何年だったか
+リモートワークが流行ったのは
+あの頃はまさか
+こんな形で仕事することになるとは思わなかったな
+虫の中だぜ
+まあいいじゃないか
+温かいし
+上司の機嫌も
+虫が調整してくれるようになって安定した
+フェロモン効果ってやつか
+昔は大変だったよな
+満員電車に乗って
+毎朝会社まで移動してたんだから
+人間は極力動かないほうが
+世界には優しいのさ
+ところで
+お前
+最後に外へ出たのいつだっけ
+……
+いつだったかな</t>
+  </si>
+  <si>
+    <t>I think it was sometime in the 2000s
+when remote work became popular
+Back then
+I never imagined we'd end up working like this
+Inside a bug
+Well, it's not so bad
+It's warm in here
+Even the boss's mood is stable now
+The bug seems to regulate it for him
+Must be the pheromones
+Things were tough back then
+We used to cram onto packed trains
+and commute to the office every morning
+The less humans move around
+the better it is for the planet
+By the way
+When was the last time
+you went outside?
+...
+When was it again?</t>
+  </si>
+  <si>
+    <t>068</t>
+  </si>
+  <si>
+    <t>第八触手線</t>
+  </si>
+  <si>
+    <t>No. 8 Tentacle Line</t>
+  </si>
+  <si>
+    <t>26.09.02</t>
+  </si>
+  <si>
+    <t>月面鉄道に配属されてもう七年になる
+今日も朝から第八触手の動きが悪い
+おい
+ポイント切り替わってないぞ
+ああ
+昨日から機嫌悪いんですよ
+餌は？
+貨物三本通したらやる予定です
+そうか
+月面鉄道は人間が作ったものではない
+地下に棲む巨大生物の神経が地表へ伸びたものだ
+我々はその上にレールを敷き列車を走らせている
+神経だからたまに動く
+昨日まで東へ伸びていた路線が
+朝には北を向いていることもある
+まあ
+七年もいれば慣れる
+ガタンゴトン
+お
+第八触手戻りました
+うん
+じゃあ終電までこのまま走らせよう
+餌の準備は？
+ええ
+もう刻んで準備できてます</t>
+  </si>
+  <si>
+    <t>I’ve been assigned to the Lunar Railway for seven years now
+The Eighth Tentacle has been acting up again since this morning
+Hey
+the switch hasn’t changed
+Yeah
+it’s been in a bad mood since yesterday
+What about its food?
+We’re planning to feed it after three freight trains pass
+I see
+The Lunar Railway wasn’t built by humans
+It’s actually the nerves of a giant creature living underground
+extending all the way up to the surface
+We laid tracks over them
+and run our trains on top
+They’re nerves
+so they move sometimes
+A line that was running east yesterday
+might be pointing north by morning
+Well
+after seven years you get used to it
+Clackety-clack
+Oh
+The Eighth Tentacle is back in place
+Yeah
+Let’s keep the trains running like this until the last one tonight
+Is the food ready?
+Yep
+it’s already chopped up and ready to go</t>
+  </si>
+  <si>
+    <t>069</t>
+  </si>
+  <si>
+    <t>高貴なもの</t>
+  </si>
+  <si>
+    <t>Noble Things</t>
+  </si>
+  <si>
+    <t>26.09.08</t>
+  </si>
+  <si>
+    <t>今日の品質はどうかな？
+ああ
+いつもどおりの純度でできているようだ
+粒も細かい
+南側は今年も当たりだな
+北側の坑道産は？
+だめだ
+最近また値が落ちた
+商人は結晶を光にかざした
+この地下では昔から
+細かな結晶が採れる
+街では高値で取引されているが
+どうやってできるのか
+……
+糞なのだ
+あの糞でできている
+この世にある
+綺麗で高貴なものというのは
+だいたい何かの排泄物で
+できているものだ
+人間とは
+そんなものなのだよ</t>
+  </si>
+  <si>
+    <t>How's the quality today?
+Yeah.
+Looks like the purity is as good as usual.
+The grains are fine, too.
+The south side came out well again this year.
+What about the ones from the northern mine?
+No good.
+The price has dropped again lately.
+The merchant held a crystal up to the light.
+Fine crystals have been mined
+beneath this ground for generations.
+They fetch a high price in the city.
+But how are they made?
+...
+It's shit.
+They're made from that thing's shit.
+The beautiful
+and precious things in this world
+are usually made
+from something's waste.
+That's just
+how humans are.</t>
   </si>
 </sst>
 </file>
@@ -4607,7 +4846,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="22.63"/>
+    <col customWidth="1" min="2" max="2" width="18.38"/>
     <col customWidth="1" min="5" max="5" width="68.63"/>
     <col customWidth="1" min="6" max="6" width="47.88"/>
   </cols>
@@ -7187,12 +7426,24 @@
       <c r="Y66" s="3"/>
     </row>
     <row r="67">
-      <c r="A67" s="4"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
+      <c r="A67" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>393</v>
+      </c>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
@@ -7214,12 +7465,24 @@
       <c r="Y67" s="3"/>
     </row>
     <row r="68">
-      <c r="A68" s="4"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
+      <c r="A68" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>399</v>
+      </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
@@ -7241,12 +7504,24 @@
       <c r="Y68" s="3"/>
     </row>
     <row r="69">
-      <c r="A69" s="4"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
+      <c r="A69" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>405</v>
+      </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
@@ -7268,12 +7543,24 @@
       <c r="Y69" s="3"/>
     </row>
     <row r="70">
-      <c r="A70" s="4"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
+      <c r="A70" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>411</v>
+      </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
